--- a/NApendling.xlsx
+++ b/NApendling.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">regionkod</t>
   </si>
@@ -20,9 +20,6 @@
     <t xml:space="preserve">region</t>
   </si>
   <si>
-    <t xml:space="preserve">utbildning</t>
-  </si>
-  <si>
     <t xml:space="preserve">kön</t>
   </si>
   <si>
@@ -41,13 +38,10 @@
     <t xml:space="preserve">Stockholms län</t>
   </si>
   <si>
-    <t xml:space="preserve">samtliga utbildningsgrupper</t>
-  </si>
-  <si>
     <t xml:space="preserve">totalt</t>
   </si>
   <si>
-    <t xml:space="preserve">2023</t>
+    <t xml:space="preserve">2024</t>
   </si>
   <si>
     <t xml:space="preserve">Andel utpendling</t>
@@ -521,974 +515,845 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.85673440229401</v>
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.00303582523988</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="n">
-        <v>9.21976169736383</v>
+      <c r="F3" t="n">
+        <v>9.27965547300738</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="n">
-        <v>25.7688358806037</v>
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>25.8433718920356</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13.4002767934165</v>
+      <c r="F5" t="n">
+        <v>13.714533246697</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" t="n">
-        <v>20.5469143943214</v>
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>20.6546665410109</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" t="n">
-        <v>10.2603194630637</v>
+      <c r="F7" t="n">
+        <v>10.4865861005777</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6.32514326379265</v>
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6.37529033200318</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.1690143515271</v>
+      <c r="F9" t="n">
+        <v>5.24722261955848</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6.54216111972173</v>
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6.64218978537954</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7.2701019551679</v>
+      <c r="F11" t="n">
+        <v>7.24136499255577</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" t="n">
-        <v>8.27135077699562</v>
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8.12905390292999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" t="n">
-        <v>12.7346818435489</v>
+      <c r="F13" t="n">
+        <v>12.8186352541653</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" t="n">
-        <v>7.7064581827738</v>
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8.04988338331191</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.12229244054224</v>
+      <c r="F15" t="n">
+        <v>5.12817994303114</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7.50716764750264</v>
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7.58578478252553</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
       </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.99404808520636</v>
+      <c r="F17" t="n">
+        <v>3.78365461207583</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" t="n">
-        <v>12.37411535611</v>
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12.4235592296244</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
       </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" t="n">
-        <v>9.48964274992495</v>
+      <c r="F19" t="n">
+        <v>9.55410135443616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" t="n">
-        <v>7.38304973117428</v>
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8.01596047036707</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3.68878908410821</v>
+      <c r="F21" t="n">
+        <v>3.82367150159458</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" t="n">
-        <v>23.2553077060978</v>
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.4085870696286</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
       </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" t="n">
-        <v>11.4327725193773</v>
+      <c r="F23" t="n">
+        <v>11.5814213766088</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" t="n">
-        <v>5.07913986213608</v>
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.23353578196695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" t="s">
         <v>11</v>
       </c>
-      <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5.97629810979036</v>
+      <c r="F25" t="n">
+        <v>5.95022654399698</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" t="n">
-        <v>8.59988171166419</v>
+        <v>10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8.96232137224931</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" t="s">
         <v>11</v>
       </c>
-      <c r="F27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" t="n">
-        <v>4.69134156200255</v>
+      <c r="F27" t="n">
+        <v>4.78329273244011</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" t="n">
-        <v>7.49949215009141</v>
+        <v>10</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7.60375886679935</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
       </c>
-      <c r="F29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" t="n">
-        <v>8.11214010305935</v>
+      <c r="F29" t="n">
+        <v>8.40506182743244</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" t="n">
-        <v>15.6879978905819</v>
+        <v>10</v>
+      </c>
+      <c r="F30" t="n">
+        <v>15.4336971339609</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
       </c>
-      <c r="F31" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" t="n">
-        <v>11.1733113340966</v>
+      <c r="F31" t="n">
+        <v>11.3557573605263</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" t="n">
-        <v>6.90740090075702</v>
+        <v>10</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.86268994945396</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E33" t="s">
         <v>11</v>
       </c>
-      <c r="F33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" t="n">
-        <v>5.55285501328667</v>
+      <c r="F33" t="n">
+        <v>5.61577237228922</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" t="n">
-        <v>8.11791456354518</v>
+        <v>10</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8.30429260031266</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E35" t="s">
         <v>11</v>
       </c>
-      <c r="F35" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" t="n">
-        <v>6.20066344547153</v>
+      <c r="F35" t="n">
+        <v>6.21189913055065</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" t="n">
-        <v>5.28398379901824</v>
+        <v>10</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.38354724911807</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E37" t="s">
         <v>11</v>
       </c>
-      <c r="F37" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" t="n">
-        <v>4.65489868197319</v>
+      <c r="F37" t="n">
+        <v>4.58411785298654</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" t="n">
-        <v>7.04878409707493</v>
+        <v>10</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7.21891534391534</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E39" t="s">
         <v>11</v>
       </c>
-      <c r="F39" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" t="n">
-        <v>4.11641988500483</v>
+      <c r="F39" t="n">
+        <v>4.11469191073443</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" t="n">
-        <v>4.57363336205516</v>
+        <v>10</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.64406882806676</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E41" t="s">
         <v>11</v>
       </c>
-      <c r="F41" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" t="n">
-        <v>3.70498614958449</v>
+      <c r="F41" t="n">
+        <v>3.95730857046538</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" t="s">
-        <v>12</v>
-      </c>
-      <c r="G42" t="n">
-        <v>4.07999090614972</v>
+        <v>10</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.13307775122758</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E43" t="s">
         <v>11</v>
       </c>
-      <c r="F43" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" t="n">
-        <v>3.37279565914416</v>
+      <c r="F43" t="n">
+        <v>3.68882010516875</v>
       </c>
     </row>
   </sheetData>
